--- a/config/template.xlsx
+++ b/config/template.xlsx
@@ -1,46 +1,131 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\plc-custom\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF45A861-9DAA-43CF-AD15-E76E816DE418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="2535" windowWidth="17640" windowHeight="11850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>G1 Output</t>
+  </si>
+  <si>
+    <t>G2 Output</t>
+  </si>
+  <si>
+    <t>G3 Output</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>p3</t>
+  </si>
+  <si>
+    <t>p4</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
+    <t>p6</t>
+  </si>
+  <si>
+    <t>p7</t>
+  </si>
+  <si>
+    <t>p8</t>
+  </si>
+  <si>
+    <t>p9</t>
+  </si>
+  <si>
+    <t>OK/NG</t>
+  </si>
+  <si>
+    <t>Danh nghia</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001976D2"/>
-        <bgColor rgb="001976D2"/>
+        <fgColor rgb="FF1976D2"/>
+        <bgColor rgb="FF1976D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,84 +141,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,148 +448,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="11" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>G1 Output</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>G2 Output</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>G3 Output</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>p1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <f>(B2+B3+B4+B5)/4</f>
-        <v/>
-      </c>
-      <c r="L2">
-        <f>(B6+B7+B8+B9)/4</f>
-        <v/>
-      </c>
-      <c r="M2">
-        <f>B10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>p3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>p6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>p7</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>p8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>p9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <f>B2-E2</f>
+        <v>2.6589999999999998</v>
+      </c>
+      <c r="E2">
+        <v>-2.6589999999999998</v>
+      </c>
+      <c r="F2">
+        <v>0.35</v>
+      </c>
+      <c r="G2">
+        <v>0.15</v>
+      </c>
+      <c r="H2" s="2">
+        <f>IF(AND(C2&lt;=F2,C2&gt;=G2),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <f>IF(SUM(H2:H5)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <f>IF(SUM(H6:H9)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <f>H10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C10" si="0">B3-E3</f>
+        <v>1.643</v>
+      </c>
+      <c r="E3">
+        <v>-1.643</v>
+      </c>
+      <c r="F3">
+        <v>0.35</v>
+      </c>
+      <c r="G3">
+        <v>0.15</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H10" si="1">IF(AND(C3&lt;=F3,C3&gt;=G3),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1.968</v>
+      </c>
+      <c r="E4">
+        <v>-1.968</v>
+      </c>
+      <c r="F4">
+        <v>0.35</v>
+      </c>
+      <c r="G4">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="E5">
+        <v>-1.8140000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.35</v>
+      </c>
+      <c r="G5">
+        <v>0.15</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G6">
+        <v>-0.08</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G7">
+        <v>-0.08</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G8">
+        <v>-0.08</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>-4</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G9">
+        <v>-0.08</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-7.1599999999999997E-2</v>
+      </c>
+      <c r="E10">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="F10">
+        <v>0.1</v>
+      </c>
+      <c r="G10">
+        <v>-0.1</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
